--- a/Luban/Config/Datas/#ConditionConfig.xlsx
+++ b/Luban/Config/Datas/#ConditionConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2431892-C6D5-4BD7-B553-A52DDE4F885C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4EA6447-10A1-4386-BE9C-71C27AB51F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12330" yWindow="3465" windowWidth="25695" windowHeight="13080" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,78 +24,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Admin</author>
-  </authors>
-  <commentList>
-    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{31693E38-24A4-47D2-B27B-C8AB67E9FCF7}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Admin:
--2小于</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
--1小于等于
-0等于
-1大于等于
-2大于</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{C4206D52-59B6-491F-863D-BFDD0CF59D4B}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
--2小于
--1小于等于
-0等于
-1大于等于
-2大于</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -125,10 +55,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>处理器代码名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -137,23 +63,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ParamList</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(list#sep=,),float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>比较符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果是释放技能扳机就随便填</t>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckTest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数描述</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -161,7 +79,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,27 +100,6 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -228,12 +125,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -554,224 +448,207 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:H51"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="33.75" style="2" customWidth="1"/>
-    <col min="4" max="4" width="32" style="1" customWidth="1"/>
-    <col min="5" max="5" width="91.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.75" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="33.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="91.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.75" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D17" s="2"/>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="F29" s="2"/>
-    </row>
-    <row r="30" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="F31" s="2"/>
-    </row>
-    <row r="32" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="F32" s="2"/>
-    </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F33" s="2"/>
-    </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F34" s="2"/>
-    </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F35" s="2"/>
-    </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F36" s="2"/>
-    </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F37" s="2"/>
-    </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F38" s="2"/>
-    </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F39" s="2"/>
-    </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F40" s="2"/>
-    </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F41" s="2"/>
-    </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F42" s="2"/>
-    </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F43" s="2"/>
-    </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F44" s="2"/>
-    </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F45" s="2"/>
-    </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F46" s="2"/>
-    </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F47" s="2"/>
-    </row>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F48" s="2"/>
-    </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F49" s="2"/>
-    </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F50" s="2"/>
-    </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F51" s="2"/>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E26" s="1"/>
+    </row>
+    <row r="27" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E27" s="1"/>
+    </row>
+    <row r="28" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E28" s="1"/>
+    </row>
+    <row r="29" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E30" s="1"/>
+    </row>
+    <row r="31" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E37" s="1"/>
+    </row>
+    <row r="38" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E38" s="1"/>
+    </row>
+    <row r="39" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E39" s="1"/>
+    </row>
+    <row r="40" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E40" s="1"/>
+    </row>
+    <row r="41" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E42" s="1"/>
+    </row>
+    <row r="43" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E43" s="1"/>
+    </row>
+    <row r="44" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E44" s="1"/>
+    </row>
+    <row r="45" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E45" s="1"/>
+    </row>
+    <row r="46" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E46" s="1"/>
+    </row>
+    <row r="47" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E47" s="1"/>
+    </row>
+    <row r="48" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E48" s="1"/>
+    </row>
+    <row r="49" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E49" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>